--- a/backtest_runs/20260410_193731/by_symbol/ICL/ICL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ICL/ICL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-4501.620000000003</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>95498.38</v>
@@ -633,7 +633,7 @@
         <v>-3312.989999999982</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>92185.39000000001</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>92185.39000000001</v>
@@ -817,7 +817,7 @@
         <v>-1036.890000000003</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>94124.29000000001</v>
@@ -906,10 +906,10 @@
         </is>
       </c>
       <c r="I10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>94124.29000000001</v>
@@ -1093,7 +1093,7 @@
         <v>-2267.669999999998</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>94882.99000000002</v>
@@ -1185,7 +1185,7 @@
         <v>-1938.899999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>95852.44000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-1154.910000000004</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>95414.08000000002</v>
@@ -1415,7 +1415,7 @@
         <v>-876.7200000000053</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>98718.64000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-3582.75</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>95135.89000000001</v>
